--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29 11:18</t>
+    <t xml:space="preserve">2026-08-19 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:19</t>
+    <t xml:space="preserve">2026-08-20 12:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 12:39</t>
+    <t xml:space="preserve">2026-08-28 15:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:07</t>
+    <t xml:space="preserve">2026-08-29 05:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,13 +474,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>44.53</v>
+        <v>89.06</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>41.59</v>
+        <v>83.17</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2.94</v>
+        <v>5.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_atacama.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:43</t>
+    <t xml:space="preserve">2026-09-07 11:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
